--- a/Methane/Methane_Bio_Brownfield_Patagonien/Datenbank.xlsx
+++ b/Methane/Methane_Bio_Brownfield_Patagonien/Datenbank.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\01-Arbeit\06-FENES\09-P2X3\FENES_P2X\Methane\Methane_Bio_Brownfield_Patagonien\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D156BA5-660F-444B-B36F-5D696B627D2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBD1ECD5-96B4-4BFB-8D5E-4A9E77F44479}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2354,7 +2354,7 @@
         <v>78</v>
       </c>
       <c r="E50" s="26">
-        <v>-1E-4</v>
+        <v>0</v>
       </c>
       <c r="F50" s="25" t="s">
         <v>19</v>
@@ -3829,6 +3829,11 @@
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="B61:B70"/>
+    <mergeCell ref="A71:A80"/>
+    <mergeCell ref="B75:B77"/>
+    <mergeCell ref="B71:B74"/>
+    <mergeCell ref="B48:B50"/>
     <mergeCell ref="B105:B106"/>
     <mergeCell ref="A81:A106"/>
     <mergeCell ref="A2:A22"/>
@@ -3845,11 +3850,6 @@
     <mergeCell ref="B100:B104"/>
     <mergeCell ref="A45:A70"/>
     <mergeCell ref="B51:B60"/>
-    <mergeCell ref="B61:B70"/>
-    <mergeCell ref="A71:A80"/>
-    <mergeCell ref="B75:B77"/>
-    <mergeCell ref="B71:B74"/>
-    <mergeCell ref="B48:B50"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Methane/Methane_Bio_Brownfield_Patagonien/Datenbank.xlsx
+++ b/Methane/Methane_Bio_Brownfield_Patagonien/Datenbank.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\01-Arbeit\06-FENES\09-P2X3\FENES_P2X\Methane\Methane_Bio_Brownfield_Patagonien\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hem38994\Documents\GitHub\FENES_P2X\Methane\Methane_Bio_Brownfield_Patagonien\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBD1ECD5-96B4-4BFB-8D5E-4A9E77F44479}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71C82A49-29AA-4008-AE75-DB62C0BC2CAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Datenauswahl" sheetId="1" r:id="rId1"/>
@@ -995,10 +995,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
-    <numFmt numFmtId="44" formatCode="_-&quot;€&quot;\ * #,##0.00_-;\-&quot;€&quot;\ * #,##0.00_-;_-&quot;€&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="0.0000"/>
-    <numFmt numFmtId="165" formatCode="0.000"/>
-    <numFmt numFmtId="166" formatCode="0.00000"/>
+    <numFmt numFmtId="164" formatCode="_-&quot;€&quot;\ * #,##0.00_-;\-&quot;€&quot;\ * #,##0.00_-;_-&quot;€&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="0.0000"/>
+    <numFmt numFmtId="166" formatCode="0.000"/>
+    <numFmt numFmtId="167" formatCode="0.00000"/>
   </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
     <font>
@@ -1130,41 +1130,41 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -1180,9 +1180,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1552,7 +1549,7 @@
       <c r="A2" s="34" t="s">
         <v>70</v>
       </c>
-      <c r="B2" s="45" t="s">
+      <c r="B2" s="44" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="7" t="s">
@@ -1570,7 +1567,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="35"/>
-      <c r="B3" s="43"/>
+      <c r="B3" s="42"/>
       <c r="C3" s="6" t="s">
         <v>84</v>
       </c>
@@ -1586,7 +1583,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="35"/>
-      <c r="B4" s="43"/>
+      <c r="B4" s="42"/>
       <c r="C4" s="6" t="s">
         <v>10</v>
       </c>
@@ -1594,7 +1591,7 @@
         <v>26</v>
       </c>
       <c r="E4" s="10">
-        <v>1000</v>
+        <v>1500</v>
       </c>
       <c r="F4" s="6" t="s">
         <v>83</v>
@@ -1602,7 +1599,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="35"/>
-      <c r="B5" s="43"/>
+      <c r="B5" s="42"/>
       <c r="C5" s="6" t="s">
         <v>11</v>
       </c>
@@ -1618,7 +1615,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="35"/>
-      <c r="B6" s="43"/>
+      <c r="B6" s="42"/>
       <c r="C6" s="6" t="s">
         <v>13</v>
       </c>
@@ -1634,7 +1631,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="35"/>
-      <c r="B7" s="43"/>
+      <c r="B7" s="42"/>
       <c r="C7" s="6" t="s">
         <v>15</v>
       </c>
@@ -1650,7 +1647,7 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="35"/>
-      <c r="B8" s="46" t="s">
+      <c r="B8" s="45" t="s">
         <v>243</v>
       </c>
       <c r="C8" s="13" t="s">
@@ -1669,7 +1666,7 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="35"/>
-      <c r="B9" s="43"/>
+      <c r="B9" s="42"/>
       <c r="C9" s="6" t="s">
         <v>85</v>
       </c>
@@ -1685,7 +1682,7 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="35"/>
-      <c r="B10" s="43"/>
+      <c r="B10" s="42"/>
       <c r="C10" s="6" t="s">
         <v>10</v>
       </c>
@@ -1701,7 +1698,7 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="35"/>
-      <c r="B11" s="43"/>
+      <c r="B11" s="42"/>
       <c r="C11" s="6" t="s">
         <v>11</v>
       </c>
@@ -1717,7 +1714,7 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="35"/>
-      <c r="B12" s="43"/>
+      <c r="B12" s="42"/>
       <c r="C12" s="6" t="s">
         <v>86</v>
       </c>
@@ -1733,7 +1730,7 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="35"/>
-      <c r="B13" s="43"/>
+      <c r="B13" s="42"/>
       <c r="C13" s="6" t="s">
         <v>228</v>
       </c>
@@ -1749,7 +1746,7 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="35"/>
-      <c r="B14" s="43"/>
+      <c r="B14" s="42"/>
       <c r="C14" s="6" t="s">
         <v>13</v>
       </c>
@@ -1765,7 +1762,7 @@
     </row>
     <row r="15" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="35"/>
-      <c r="B15" s="47"/>
+      <c r="B15" s="46"/>
       <c r="C15" s="15" t="s">
         <v>15</v>
       </c>
@@ -1783,7 +1780,7 @@
       <c r="A16" s="34" t="s">
         <v>71</v>
       </c>
-      <c r="B16" s="38" t="s">
+      <c r="B16" s="37" t="s">
         <v>3</v>
       </c>
       <c r="C16" s="7" t="s">
@@ -1801,7 +1798,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" s="35"/>
-      <c r="B17" s="39"/>
+      <c r="B17" s="38"/>
       <c r="C17" s="6" t="s">
         <v>11</v>
       </c>
@@ -1817,7 +1814,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="35"/>
-      <c r="B18" s="39"/>
+      <c r="B18" s="38"/>
       <c r="C18" s="6" t="s">
         <v>13</v>
       </c>
@@ -1833,7 +1830,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" s="35"/>
-      <c r="B19" s="39"/>
+      <c r="B19" s="38"/>
       <c r="C19" s="6" t="s">
         <v>20</v>
       </c>
@@ -1849,7 +1846,7 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" s="35"/>
-      <c r="B20" s="39"/>
+      <c r="B20" s="38"/>
       <c r="C20" s="6" t="s">
         <v>35</v>
       </c>
@@ -1865,7 +1862,7 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" s="35"/>
-      <c r="B21" s="39"/>
+      <c r="B21" s="38"/>
       <c r="C21" s="6" t="s">
         <v>36</v>
       </c>
@@ -1881,7 +1878,7 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" s="35"/>
-      <c r="B22" s="39"/>
+      <c r="B22" s="38"/>
       <c r="C22" s="6" t="s">
         <v>15</v>
       </c>
@@ -1897,7 +1894,7 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" s="35"/>
-      <c r="B23" s="40"/>
+      <c r="B23" s="39"/>
       <c r="C23" s="15" t="s">
         <v>88</v>
       </c>
@@ -1913,7 +1910,7 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" s="35"/>
-      <c r="B24" s="41" t="s">
+      <c r="B24" s="40" t="s">
         <v>200</v>
       </c>
       <c r="C24" s="13" t="s">
@@ -1931,7 +1928,7 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" s="35"/>
-      <c r="B25" s="43"/>
+      <c r="B25" s="42"/>
       <c r="C25" s="6" t="s">
         <v>21</v>
       </c>
@@ -1948,7 +1945,7 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" s="35"/>
-      <c r="B26" s="43"/>
+      <c r="B26" s="42"/>
       <c r="C26" s="6" t="s">
         <v>16</v>
       </c>
@@ -1964,7 +1961,7 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" s="35"/>
-      <c r="B27" s="43"/>
+      <c r="B27" s="42"/>
       <c r="C27" s="6" t="s">
         <v>17</v>
       </c>
@@ -1980,7 +1977,7 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" s="35"/>
-      <c r="B28" s="43"/>
+      <c r="B28" s="42"/>
       <c r="C28" s="6" t="s">
         <v>35</v>
       </c>
@@ -1996,7 +1993,7 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" s="35"/>
-      <c r="B29" s="43"/>
+      <c r="B29" s="42"/>
       <c r="C29" s="6" t="s">
         <v>36</v>
       </c>
@@ -2012,7 +2009,7 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" s="35"/>
-      <c r="B30" s="43"/>
+      <c r="B30" s="42"/>
       <c r="C30" s="6" t="s">
         <v>89</v>
       </c>
@@ -2028,7 +2025,7 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" s="35"/>
-      <c r="B31" s="43"/>
+      <c r="B31" s="42"/>
       <c r="C31" s="6" t="s">
         <v>88</v>
       </c>
@@ -2044,7 +2041,7 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" s="35"/>
-      <c r="B32" s="43"/>
+      <c r="B32" s="42"/>
       <c r="C32" s="6" t="s">
         <v>13</v>
       </c>
@@ -2060,7 +2057,7 @@
     </row>
     <row r="33" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="36"/>
-      <c r="B33" s="44"/>
+      <c r="B33" s="43"/>
       <c r="C33" s="19" t="s">
         <v>15</v>
       </c>
@@ -2095,7 +2092,7 @@
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A35" s="37"/>
+      <c r="A35" s="35"/>
       <c r="B35" s="30" t="s">
         <v>279</v>
       </c>
@@ -2114,7 +2111,7 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" s="35"/>
-      <c r="B36" s="41" t="s">
+      <c r="B36" s="40" t="s">
         <v>4</v>
       </c>
       <c r="C36" s="13" t="s">
@@ -2132,7 +2129,7 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" s="35"/>
-      <c r="B37" s="39"/>
+      <c r="B37" s="38"/>
       <c r="C37" s="6" t="s">
         <v>10</v>
       </c>
@@ -2148,7 +2145,7 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" s="35"/>
-      <c r="B38" s="39"/>
+      <c r="B38" s="38"/>
       <c r="C38" s="6" t="s">
         <v>17</v>
       </c>
@@ -2164,7 +2161,7 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" s="35"/>
-      <c r="B39" s="39"/>
+      <c r="B39" s="38"/>
       <c r="C39" s="6" t="s">
         <v>18</v>
       </c>
@@ -2180,7 +2177,7 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40" s="35"/>
-      <c r="B40" s="39"/>
+      <c r="B40" s="38"/>
       <c r="C40" s="6" t="s">
         <v>13</v>
       </c>
@@ -2196,7 +2193,7 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41" s="35"/>
-      <c r="B41" s="39"/>
+      <c r="B41" s="38"/>
       <c r="C41" s="6" t="s">
         <v>68</v>
       </c>
@@ -2212,7 +2209,7 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42" s="35"/>
-      <c r="B42" s="40"/>
+      <c r="B42" s="39"/>
       <c r="C42" s="15" t="s">
         <v>15</v>
       </c>
@@ -2228,7 +2225,7 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43" s="35"/>
-      <c r="B43" s="41" t="s">
+      <c r="B43" s="40" t="s">
         <v>5</v>
       </c>
       <c r="C43" s="13" t="s">
@@ -2246,7 +2243,7 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A44" s="35"/>
-      <c r="B44" s="39"/>
+      <c r="B44" s="38"/>
       <c r="C44" s="6" t="s">
         <v>10</v>
       </c>
@@ -2262,7 +2259,7 @@
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A45" s="35"/>
-      <c r="B45" s="39"/>
+      <c r="B45" s="38"/>
       <c r="C45" s="6" t="s">
         <v>17</v>
       </c>
@@ -2278,7 +2275,7 @@
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A46" s="35"/>
-      <c r="B46" s="39"/>
+      <c r="B46" s="38"/>
       <c r="C46" s="6" t="s">
         <v>18</v>
       </c>
@@ -2294,7 +2291,7 @@
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A47" s="35"/>
-      <c r="B47" s="39"/>
+      <c r="B47" s="38"/>
       <c r="C47" s="6" t="s">
         <v>13</v>
       </c>
@@ -2310,7 +2307,7 @@
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A48" s="35"/>
-      <c r="B48" s="39"/>
+      <c r="B48" s="38"/>
       <c r="C48" s="6" t="s">
         <v>68</v>
       </c>
@@ -2326,7 +2323,7 @@
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A49" s="36"/>
-      <c r="B49" s="42"/>
+      <c r="B49" s="41"/>
       <c r="C49" s="19" t="s">
         <v>15</v>
       </c>
@@ -2453,7 +2450,7 @@
       <c r="A2" s="34" t="s">
         <v>70</v>
       </c>
-      <c r="B2" s="45" t="s">
+      <c r="B2" s="44" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="7" t="s">
@@ -2469,7 +2466,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="35"/>
-      <c r="B3" s="43"/>
+      <c r="B3" s="42"/>
       <c r="C3" s="6" t="s">
         <v>107</v>
       </c>
@@ -2483,7 +2480,7 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="35"/>
-      <c r="B4" s="43"/>
+      <c r="B4" s="42"/>
       <c r="C4" s="6" t="s">
         <v>84</v>
       </c>
@@ -2497,7 +2494,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="35"/>
-      <c r="B5" s="43"/>
+      <c r="B5" s="42"/>
       <c r="C5" s="6" t="s">
         <v>138</v>
       </c>
@@ -2511,7 +2508,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="35"/>
-      <c r="B6" s="43"/>
+      <c r="B6" s="42"/>
       <c r="C6" s="6" t="s">
         <v>141</v>
       </c>
@@ -2525,7 +2522,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="35"/>
-      <c r="B7" s="43"/>
+      <c r="B7" s="42"/>
       <c r="C7" s="6" t="s">
         <v>155</v>
       </c>
@@ -2539,7 +2536,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="35"/>
-      <c r="B8" s="43"/>
+      <c r="B8" s="42"/>
       <c r="C8" s="6" t="s">
         <v>195</v>
       </c>
@@ -2553,7 +2550,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="35"/>
-      <c r="B9" s="43"/>
+      <c r="B9" s="42"/>
       <c r="C9" s="6" t="s">
         <v>167</v>
       </c>
@@ -2567,7 +2564,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="35"/>
-      <c r="B10" s="43"/>
+      <c r="B10" s="42"/>
       <c r="C10" s="6" t="s">
         <v>187</v>
       </c>
@@ -2581,12 +2578,12 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="35"/>
-      <c r="B11" s="43"/>
+      <c r="B11" s="42"/>
       <c r="E11" s="11"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="35"/>
-      <c r="B12" s="46" t="s">
+      <c r="B12" s="45" t="s">
         <v>243</v>
       </c>
       <c r="C12" s="13" t="s">
@@ -2602,7 +2599,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="35"/>
-      <c r="B13" s="43"/>
+      <c r="B13" s="42"/>
       <c r="C13" s="6" t="s">
         <v>229</v>
       </c>
@@ -2616,7 +2613,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="35"/>
-      <c r="B14" s="43"/>
+      <c r="B14" s="42"/>
       <c r="C14" s="6" t="s">
         <v>139</v>
       </c>
@@ -2630,7 +2627,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="35"/>
-      <c r="B15" s="43"/>
+      <c r="B15" s="42"/>
       <c r="C15" s="6" t="s">
         <v>230</v>
       </c>
@@ -2644,7 +2641,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="35"/>
-      <c r="B16" s="43"/>
+      <c r="B16" s="42"/>
       <c r="C16" s="6" t="s">
         <v>84</v>
       </c>
@@ -2658,7 +2655,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" s="35"/>
-      <c r="B17" s="43"/>
+      <c r="B17" s="42"/>
       <c r="C17" s="6" t="s">
         <v>141</v>
       </c>
@@ -2672,7 +2669,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="35"/>
-      <c r="B18" s="43"/>
+      <c r="B18" s="42"/>
       <c r="C18" s="6" t="s">
         <v>155</v>
       </c>
@@ -2686,7 +2683,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" s="35"/>
-      <c r="B19" s="43"/>
+      <c r="B19" s="42"/>
       <c r="C19" s="6" t="s">
         <v>195</v>
       </c>
@@ -2700,7 +2697,7 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" s="35"/>
-      <c r="B20" s="43"/>
+      <c r="B20" s="42"/>
       <c r="C20" s="6" t="s">
         <v>167</v>
       </c>
@@ -2714,7 +2711,7 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" s="35"/>
-      <c r="B21" s="43"/>
+      <c r="B21" s="42"/>
       <c r="C21" s="6" t="s">
         <v>187</v>
       </c>
@@ -2728,7 +2725,7 @@
     </row>
     <row r="22" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="35"/>
-      <c r="B22" s="47"/>
+      <c r="B22" s="46"/>
       <c r="C22" s="15"/>
       <c r="D22" s="15"/>
       <c r="E22" s="16"/>
@@ -2738,7 +2735,7 @@
       <c r="A23" s="34" t="s">
         <v>71</v>
       </c>
-      <c r="B23" s="38" t="s">
+      <c r="B23" s="37" t="s">
         <v>3</v>
       </c>
       <c r="C23" s="7" t="s">
@@ -2754,7 +2751,7 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" s="35"/>
-      <c r="B24" s="39"/>
+      <c r="B24" s="38"/>
       <c r="C24" s="6" t="s">
         <v>111</v>
       </c>
@@ -2768,7 +2765,7 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" s="35"/>
-      <c r="B25" s="39"/>
+      <c r="B25" s="38"/>
       <c r="C25" s="6" t="s">
         <v>135</v>
       </c>
@@ -2782,7 +2779,7 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" s="35"/>
-      <c r="B26" s="39"/>
+      <c r="B26" s="38"/>
       <c r="C26" s="6" t="s">
         <v>136</v>
       </c>
@@ -2796,7 +2793,7 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" s="35"/>
-      <c r="B27" s="39"/>
+      <c r="B27" s="38"/>
       <c r="C27" s="6" t="s">
         <v>141</v>
       </c>
@@ -2810,7 +2807,7 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" s="35"/>
-      <c r="B28" s="39"/>
+      <c r="B28" s="38"/>
       <c r="C28" s="6" t="s">
         <v>155</v>
       </c>
@@ -2824,7 +2821,7 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" s="35"/>
-      <c r="B29" s="39"/>
+      <c r="B29" s="38"/>
       <c r="C29" s="6" t="s">
         <v>195</v>
       </c>
@@ -2838,7 +2835,7 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" s="35"/>
-      <c r="B30" s="39"/>
+      <c r="B30" s="38"/>
       <c r="C30" s="6" t="s">
         <v>167</v>
       </c>
@@ -2852,7 +2849,7 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" s="35"/>
-      <c r="B31" s="39"/>
+      <c r="B31" s="38"/>
       <c r="C31" s="6" t="s">
         <v>187</v>
       </c>
@@ -2866,7 +2863,7 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" s="35"/>
-      <c r="B32" s="40"/>
+      <c r="B32" s="39"/>
       <c r="C32" s="15"/>
       <c r="D32" s="15"/>
       <c r="E32" s="16"/>
@@ -2874,7 +2871,7 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" s="35"/>
-      <c r="B33" s="41" t="s">
+      <c r="B33" s="40" t="s">
         <v>6</v>
       </c>
       <c r="C33" s="13" t="s">
@@ -2890,7 +2887,7 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34" s="35"/>
-      <c r="B34" s="39"/>
+      <c r="B34" s="38"/>
       <c r="C34" s="6" t="s">
         <v>113</v>
       </c>
@@ -2904,7 +2901,7 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" s="35"/>
-      <c r="B35" s="43"/>
+      <c r="B35" s="42"/>
       <c r="C35" s="6" t="s">
         <v>111</v>
       </c>
@@ -2918,7 +2915,7 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" s="35"/>
-      <c r="B36" s="43"/>
+      <c r="B36" s="42"/>
       <c r="C36" s="6" t="s">
         <v>107</v>
       </c>
@@ -2932,7 +2929,7 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" s="35"/>
-      <c r="B37" s="43"/>
+      <c r="B37" s="42"/>
       <c r="C37" s="6" t="s">
         <v>126</v>
       </c>
@@ -2946,7 +2943,7 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" s="35"/>
-      <c r="B38" s="43"/>
+      <c r="B38" s="42"/>
       <c r="C38" s="6" t="s">
         <v>127</v>
       </c>
@@ -2960,7 +2957,7 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" s="35"/>
-      <c r="B39" s="43"/>
+      <c r="B39" s="42"/>
       <c r="C39" s="6" t="s">
         <v>141</v>
       </c>
@@ -2974,7 +2971,7 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40" s="35"/>
-      <c r="B40" s="43"/>
+      <c r="B40" s="42"/>
       <c r="C40" s="6" t="s">
         <v>155</v>
       </c>
@@ -2988,7 +2985,7 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41" s="35"/>
-      <c r="B41" s="43"/>
+      <c r="B41" s="42"/>
       <c r="C41" s="6" t="s">
         <v>195</v>
       </c>
@@ -3002,7 +2999,7 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42" s="35"/>
-      <c r="B42" s="43"/>
+      <c r="B42" s="42"/>
       <c r="C42" s="6" t="s">
         <v>167</v>
       </c>
@@ -3016,7 +3013,7 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43" s="35"/>
-      <c r="B43" s="43"/>
+      <c r="B43" s="42"/>
       <c r="C43" s="6" t="s">
         <v>187</v>
       </c>
@@ -3030,7 +3027,7 @@
     </row>
     <row r="44" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A44" s="36"/>
-      <c r="B44" s="44"/>
+      <c r="B44" s="43"/>
       <c r="C44" s="19"/>
       <c r="D44" s="19"/>
       <c r="E44" s="20"/>
@@ -3040,7 +3037,7 @@
       <c r="A45" s="34" t="s">
         <v>72</v>
       </c>
-      <c r="B45" s="45" t="s">
+      <c r="B45" s="44" t="s">
         <v>73</v>
       </c>
       <c r="C45" s="7" t="s">
@@ -3056,7 +3053,7 @@
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A46" s="35"/>
-      <c r="B46" s="43"/>
+      <c r="B46" s="42"/>
       <c r="C46" s="6" t="s">
         <v>153</v>
       </c>
@@ -3070,7 +3067,7 @@
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A47" s="35"/>
-      <c r="B47" s="47"/>
+      <c r="B47" s="46"/>
       <c r="C47" s="15"/>
       <c r="D47" s="15"/>
       <c r="E47" s="31"/>
@@ -3078,7 +3075,7 @@
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A48" s="35"/>
-      <c r="B48" s="43" t="s">
+      <c r="B48" s="42" t="s">
         <v>279</v>
       </c>
       <c r="C48" s="6" t="s">
@@ -3094,7 +3091,7 @@
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A49" s="35"/>
-      <c r="B49" s="43"/>
+      <c r="B49" s="42"/>
       <c r="C49" s="6" t="s">
         <v>284</v>
       </c>
@@ -3108,12 +3105,12 @@
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A50" s="35"/>
-      <c r="B50" s="43"/>
+      <c r="B50" s="42"/>
       <c r="E50" s="9"/>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A51" s="35"/>
-      <c r="B51" s="41" t="s">
+      <c r="B51" s="40" t="s">
         <v>4</v>
       </c>
       <c r="C51" s="13" t="s">
@@ -3129,7 +3126,7 @@
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A52" s="35"/>
-      <c r="B52" s="39"/>
+      <c r="B52" s="38"/>
       <c r="C52" s="6" t="s">
         <v>107</v>
       </c>
@@ -3143,7 +3140,7 @@
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A53" s="35"/>
-      <c r="B53" s="39"/>
+      <c r="B53" s="38"/>
       <c r="C53" s="6" t="s">
         <v>122</v>
       </c>
@@ -3157,7 +3154,7 @@
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A54" s="35"/>
-      <c r="B54" s="39"/>
+      <c r="B54" s="38"/>
       <c r="C54" s="6" t="s">
         <v>141</v>
       </c>
@@ -3171,7 +3168,7 @@
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A55" s="35"/>
-      <c r="B55" s="39"/>
+      <c r="B55" s="38"/>
       <c r="C55" s="6" t="s">
         <v>155</v>
       </c>
@@ -3185,7 +3182,7 @@
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A56" s="35"/>
-      <c r="B56" s="39"/>
+      <c r="B56" s="38"/>
       <c r="C56" s="6" t="s">
         <v>161</v>
       </c>
@@ -3199,7 +3196,7 @@
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A57" s="35"/>
-      <c r="B57" s="39"/>
+      <c r="B57" s="38"/>
       <c r="C57" s="6" t="s">
         <v>195</v>
       </c>
@@ -3213,7 +3210,7 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A58" s="35"/>
-      <c r="B58" s="39"/>
+      <c r="B58" s="38"/>
       <c r="C58" s="6" t="s">
         <v>167</v>
       </c>
@@ -3227,7 +3224,7 @@
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A59" s="35"/>
-      <c r="B59" s="39"/>
+      <c r="B59" s="38"/>
       <c r="C59" s="6" t="s">
         <v>187</v>
       </c>
@@ -3241,11 +3238,11 @@
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A60" s="35"/>
-      <c r="B60" s="40"/>
+      <c r="B60" s="39"/>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A61" s="35"/>
-      <c r="B61" s="41" t="s">
+      <c r="B61" s="40" t="s">
         <v>5</v>
       </c>
       <c r="C61" s="13" t="s">
@@ -3261,7 +3258,7 @@
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A62" s="35"/>
-      <c r="B62" s="39"/>
+      <c r="B62" s="38"/>
       <c r="C62" s="6" t="s">
         <v>108</v>
       </c>
@@ -3275,7 +3272,7 @@
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A63" s="35"/>
-      <c r="B63" s="39"/>
+      <c r="B63" s="38"/>
       <c r="C63" s="6" t="s">
         <v>120</v>
       </c>
@@ -3289,7 +3286,7 @@
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A64" s="35"/>
-      <c r="B64" s="39"/>
+      <c r="B64" s="38"/>
       <c r="C64" s="6" t="s">
         <v>141</v>
       </c>
@@ -3303,7 +3300,7 @@
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A65" s="35"/>
-      <c r="B65" s="39"/>
+      <c r="B65" s="38"/>
       <c r="C65" s="6" t="s">
         <v>155</v>
       </c>
@@ -3317,7 +3314,7 @@
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A66" s="35"/>
-      <c r="B66" s="39"/>
+      <c r="B66" s="38"/>
       <c r="C66" s="6" t="s">
         <v>161</v>
       </c>
@@ -3331,7 +3328,7 @@
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A67" s="35"/>
-      <c r="B67" s="39"/>
+      <c r="B67" s="38"/>
       <c r="C67" s="6" t="s">
         <v>195</v>
       </c>
@@ -3345,7 +3342,7 @@
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A68" s="35"/>
-      <c r="B68" s="39"/>
+      <c r="B68" s="38"/>
       <c r="C68" s="6" t="s">
         <v>167</v>
       </c>
@@ -3359,7 +3356,7 @@
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A69" s="35"/>
-      <c r="B69" s="39"/>
+      <c r="B69" s="38"/>
       <c r="C69" s="6" t="s">
         <v>187</v>
       </c>
@@ -3373,13 +3370,13 @@
     </row>
     <row r="70" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A70" s="36"/>
-      <c r="B70" s="42"/>
+      <c r="B70" s="41"/>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A71" s="34" t="s">
         <v>76</v>
       </c>
-      <c r="B71" s="45" t="s">
+      <c r="B71" s="44" t="s">
         <v>73</v>
       </c>
       <c r="C71" s="7" t="s">
@@ -3395,7 +3392,7 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A72" s="35"/>
-      <c r="B72" s="43"/>
+      <c r="B72" s="42"/>
       <c r="C72" s="6" t="s">
         <v>227</v>
       </c>
@@ -3409,7 +3406,7 @@
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A73" s="35"/>
-      <c r="B73" s="43"/>
+      <c r="B73" s="42"/>
       <c r="C73" s="6" t="s">
         <v>150</v>
       </c>
@@ -3423,7 +3420,7 @@
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A74" s="35"/>
-      <c r="B74" s="47"/>
+      <c r="B74" s="46"/>
       <c r="C74" s="15"/>
       <c r="D74" s="15"/>
       <c r="E74" s="16"/>
@@ -3431,7 +3428,7 @@
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A75" s="35"/>
-      <c r="B75" s="46" t="s">
+      <c r="B75" s="45" t="s">
         <v>79</v>
       </c>
       <c r="C75" s="13" t="s">
@@ -3447,7 +3444,7 @@
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A76" s="35"/>
-      <c r="B76" s="43"/>
+      <c r="B76" s="42"/>
       <c r="C76" s="6" t="s">
         <v>151</v>
       </c>
@@ -3461,7 +3458,7 @@
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A77" s="35"/>
-      <c r="B77" s="47"/>
+      <c r="B77" s="46"/>
       <c r="C77" s="15"/>
       <c r="D77" s="15"/>
       <c r="E77" s="16"/>
@@ -3469,7 +3466,7 @@
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A78" s="35"/>
-      <c r="B78" s="46" t="s">
+      <c r="B78" s="45" t="s">
         <v>268</v>
       </c>
       <c r="C78" s="6" t="s">
@@ -3485,7 +3482,7 @@
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A79" s="35"/>
-      <c r="B79" s="43"/>
+      <c r="B79" s="42"/>
       <c r="C79" s="6" t="s">
         <v>270</v>
       </c>
@@ -3499,7 +3496,7 @@
     </row>
     <row r="80" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A80" s="36"/>
-      <c r="B80" s="44"/>
+      <c r="B80" s="43"/>
       <c r="C80" s="19"/>
       <c r="D80" s="19"/>
       <c r="E80" s="20"/>
@@ -3509,7 +3506,7 @@
       <c r="A81" s="34" t="s">
         <v>163</v>
       </c>
-      <c r="B81" s="45" t="s">
+      <c r="B81" s="44" t="s">
         <v>13</v>
       </c>
       <c r="C81" s="7" t="s">
@@ -3525,7 +3522,7 @@
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A82" s="35"/>
-      <c r="B82" s="43"/>
+      <c r="B82" s="42"/>
       <c r="C82" s="6" t="s">
         <v>174</v>
       </c>
@@ -3538,7 +3535,7 @@
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A83" s="35"/>
-      <c r="B83" s="47"/>
+      <c r="B83" s="46"/>
       <c r="C83" s="15"/>
       <c r="D83" s="15"/>
       <c r="E83" s="15"/>
@@ -3546,7 +3543,7 @@
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A84" s="35"/>
-      <c r="B84" s="46" t="s">
+      <c r="B84" s="45" t="s">
         <v>183</v>
       </c>
       <c r="C84" s="6" t="s">
@@ -3561,7 +3558,7 @@
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A85" s="35"/>
-      <c r="B85" s="43"/>
+      <c r="B85" s="42"/>
       <c r="C85" s="6" t="s">
         <v>181</v>
       </c>
@@ -3574,7 +3571,7 @@
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A86" s="35"/>
-      <c r="B86" s="43"/>
+      <c r="B86" s="42"/>
       <c r="C86" s="6" t="s">
         <v>177</v>
       </c>
@@ -3587,7 +3584,7 @@
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A87" s="35"/>
-      <c r="B87" s="43"/>
+      <c r="B87" s="42"/>
       <c r="C87" s="6" t="s">
         <v>179</v>
       </c>
@@ -3600,7 +3597,7 @@
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A88" s="35"/>
-      <c r="B88" s="43"/>
+      <c r="B88" s="42"/>
       <c r="C88" s="6" t="s">
         <v>182</v>
       </c>
@@ -3613,7 +3610,7 @@
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A89" s="35"/>
-      <c r="B89" s="43"/>
+      <c r="B89" s="42"/>
       <c r="C89" s="6" t="s">
         <v>190</v>
       </c>
@@ -3626,11 +3623,11 @@
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A90" s="35"/>
-      <c r="B90" s="43"/>
+      <c r="B90" s="42"/>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A91" s="35"/>
-      <c r="B91" s="46" t="s">
+      <c r="B91" s="45" t="s">
         <v>205</v>
       </c>
       <c r="C91" s="13" t="s">
@@ -3646,7 +3643,7 @@
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A92" s="35"/>
-      <c r="B92" s="43"/>
+      <c r="B92" s="42"/>
       <c r="C92" s="6" t="s">
         <v>203</v>
       </c>
@@ -3659,7 +3656,7 @@
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A93" s="35"/>
-      <c r="B93" s="43"/>
+      <c r="B93" s="42"/>
       <c r="C93" s="6" t="s">
         <v>214</v>
       </c>
@@ -3672,7 +3669,7 @@
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A94" s="35"/>
-      <c r="B94" s="43"/>
+      <c r="B94" s="42"/>
       <c r="C94" s="6" t="s">
         <v>204</v>
       </c>
@@ -3685,7 +3682,7 @@
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A95" s="35"/>
-      <c r="B95" s="43"/>
+      <c r="B95" s="42"/>
       <c r="C95" s="6" t="s">
         <v>216</v>
       </c>
@@ -3698,7 +3695,7 @@
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A96" s="35"/>
-      <c r="B96" s="43"/>
+      <c r="B96" s="42"/>
       <c r="C96" s="6" t="s">
         <v>220</v>
       </c>
@@ -3711,7 +3708,7 @@
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A97" s="35"/>
-      <c r="B97" s="43"/>
+      <c r="B97" s="42"/>
       <c r="C97" s="6" t="s">
         <v>201</v>
       </c>
@@ -3724,7 +3721,7 @@
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A98" s="35"/>
-      <c r="B98" s="43"/>
+      <c r="B98" s="42"/>
       <c r="C98" s="6" t="s">
         <v>275</v>
       </c>
@@ -3737,11 +3734,11 @@
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A99" s="35"/>
-      <c r="B99" s="43"/>
+      <c r="B99" s="42"/>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A100" s="35"/>
-      <c r="B100" s="46" t="s">
+      <c r="B100" s="45" t="s">
         <v>221</v>
       </c>
       <c r="C100" s="13" t="s">
@@ -3757,7 +3754,7 @@
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A101" s="35"/>
-      <c r="B101" s="43"/>
+      <c r="B101" s="42"/>
       <c r="C101" s="6" t="s">
         <v>224</v>
       </c>
@@ -3770,7 +3767,7 @@
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A102" s="35"/>
-      <c r="B102" s="43"/>
+      <c r="B102" s="42"/>
       <c r="C102" s="6" t="s">
         <v>232</v>
       </c>
@@ -3783,7 +3780,7 @@
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A103" s="35"/>
-      <c r="B103" s="43"/>
+      <c r="B103" s="42"/>
       <c r="C103" s="6" t="s">
         <v>234</v>
       </c>
@@ -3796,11 +3793,11 @@
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A104" s="35"/>
-      <c r="B104" s="43"/>
+      <c r="B104" s="42"/>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A105" s="35"/>
-      <c r="B105" s="46" t="s">
+      <c r="B105" s="45" t="s">
         <v>236</v>
       </c>
       <c r="C105" s="13" t="s">
@@ -3816,7 +3813,7 @@
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A106" s="35"/>
-      <c r="B106" s="43"/>
+      <c r="B106" s="42"/>
       <c r="C106" s="6" t="s">
         <v>239</v>
       </c>
@@ -3829,11 +3826,6 @@
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="B61:B70"/>
-    <mergeCell ref="A71:A80"/>
-    <mergeCell ref="B75:B77"/>
-    <mergeCell ref="B71:B74"/>
-    <mergeCell ref="B48:B50"/>
     <mergeCell ref="B105:B106"/>
     <mergeCell ref="A81:A106"/>
     <mergeCell ref="A2:A22"/>
@@ -3850,6 +3842,11 @@
     <mergeCell ref="B100:B104"/>
     <mergeCell ref="A45:A70"/>
     <mergeCell ref="B51:B60"/>
+    <mergeCell ref="B61:B70"/>
+    <mergeCell ref="A71:A80"/>
+    <mergeCell ref="B75:B77"/>
+    <mergeCell ref="B71:B74"/>
+    <mergeCell ref="B48:B50"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
